--- a/output/pdf_financials_xlsx/CUCU.xlsx
+++ b/output/pdf_financials_xlsx/CUCU.xlsx
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.364677</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.790977</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.1105</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.821125</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.05375</v>
       </c>
     </row>
     <row r="93">
@@ -3844,7 +3844,11 @@
           <t>Reserves (notes 5 and 6)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -4094,7 +4098,11 @@
           <t>Reserves (notes 5 and 6)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -4506,7 +4514,11 @@
           <t>Reserves (notes 5 and 6)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.364677</v>
       </c>

--- a/output/pdf_financials_xlsx/CUCU.xlsx
+++ b/output/pdf_financials_xlsx/CUCU.xlsx
@@ -1200,19 +1200,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.278726</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.59193</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.241697</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.070226</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.025368</v>
       </c>
     </row>
     <row r="35">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.039747</v>
+        <v>0.318473</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.02</v>
+        <v>1.61193</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.016667</v>
+        <v>0.258364</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.06551999999999999</v>
+        <v>0.135746</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.155</v>
+        <v>0.180368</v>
       </c>
     </row>
     <row r="37">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/CUCU.xlsx
+++ b/output/pdf_financials_xlsx/CUCU.xlsx
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.023297</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0.015997</v>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.126876</v>
+        <v>0.103579</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.09798</v>
@@ -6064,7 +6064,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
         <v>-0.023297</v>
       </c>
